--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1178,11 +1178,11 @@
         <v>118282701</v>
       </c>
       <c r="B6" t="n">
-        <v>57198</v>
+        <v>57273</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>118282701</v>
       </c>
       <c r="B6" t="n">
-        <v>57273</v>
+        <v>57277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
         <v>118282701</v>
       </c>
       <c r="B6" t="n">
-        <v>57282</v>
+        <v>57287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1193,11 +1193,6 @@
       <c r="E6" t="n">
         <v>100082</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Milvus milvus</t>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57603</v>
+        <v>57607</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57607</v>
+        <v>57609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57609</v>
+        <v>57612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57612</v>
+        <v>57618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57618</v>
+        <v>57603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -1287,7 +1287,7 @@
         <v>127166446</v>
       </c>
       <c r="B7" t="n">
-        <v>57603</v>
+        <v>57618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>103032082</v>
       </c>
       <c r="B2" t="n">
-        <v>56278</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561930.4411842984</v>
+        <v>561930</v>
       </c>
       <c r="R2" t="n">
-        <v>6563559.018614719</v>
+        <v>6563559</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +755,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,32 +784,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107140541</v>
+        <v>111565436</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57247</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>100038</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Skogsduva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Columba oenas</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,34 +814,30 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogskojan Långkärr, Srm</t>
+          <t>Pass 18, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561930.4411842984</v>
+        <v>561768</v>
       </c>
       <c r="R3" t="n">
-        <v>6563559.018614719</v>
+        <v>6563518</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2023-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,49 +893,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107140515</v>
+        <v>107183523</v>
       </c>
       <c r="B4" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -979,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561930.4411842984</v>
+        <v>561930</v>
       </c>
       <c r="R4" t="n">
-        <v>6563559.018614719</v>
+        <v>6563559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1012,19 +973,9 @@
           <t>2023-03-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-03-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,19 +1002,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107183523</v>
+        <v>127166446</v>
       </c>
       <c r="B5" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1086,30 +1032,30 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogskojan Långkärr, Srm</t>
+          <t>Pass 18, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561930.4411842984</v>
+        <v>561768</v>
       </c>
       <c r="R5" t="n">
-        <v>6563559.018614719</v>
+        <v>6563518</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1133,22 +1079,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,12 +1124,7 @@
         <v>118282701</v>
       </c>
       <c r="B6" t="n">
-        <v>57287</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57890</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1192,6 +1133,11 @@
       </c>
       <c r="E6" t="n">
         <v>100082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1284,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127166446</v>
+        <v>107140515</v>
       </c>
       <c r="B7" t="n">
-        <v>57618</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1327,17 +1273,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Pass 18, Srm</t>
+          <t>Skogskojan Långkärr, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561768</v>
+        <v>561930</v>
       </c>
       <c r="R7" t="n">
-        <v>6563518</v>
+        <v>6563559</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1361,22 +1307,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2023-03-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,6 +1346,242 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>107140541</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogskojan Långkärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561930</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6563559</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Julita</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-03-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Ridell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Ridell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111804071</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pass 18, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561768</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6563518</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Julita</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jan Ridell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jan Ridell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52453-2023 artfynd.xlsx
+++ b/artfynd/A 52453-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103032082</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111565436</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -999,6 +1014,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107183523</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127166446</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118282701</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140515</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1469,6 +1504,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140541</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1582,8 +1622,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111804071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>